--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0011.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0011.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hãy tận dụng thời gian này để thư giãn hoàn toàn!</t>
+          <t>Hãy nhân cơ hội này mà thoải mái tung hoành!</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bắt nhịp vũ trụ và lên đường thôi!</t>
+          <t>Bắt nhịp vũ trụ và căng buồm lên đường!</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Câu chuyện méo mó này sẽ đi đến đâu? Điều gì đang chờ đợi ở cuối con đường, ngoài chiến thắng của những người hùng...?</t>
+          <t>Câu chuyện méo mó này rồi sẽ đi về đâu? Điều gì đang chờ đợi ở cuối con đường, phía sau chiến thắng của những người anh hùng...?</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Echo Sóng Dâng</t>
+          <t>Tiếng Vang Sóng Dâng</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Kịch bản mới khai mạc tại Liên hoan Film Solaris</t>
+          <t>Kịch Bản Mới tại Liên Hoan Phim Solaris</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Resonators có thể hấp thụ Echoes bằng Terminal của mình.</t>
+          <t>Resonator có thể hấp thụ Echo bằng Thiết bị đầu cuối của mình.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Giao Lưu với nhiều Resonators và Weapons thông qua Triệu Tập. Đây là cách hiệu quả để gặp gỡ đồng minh đáng tin cậy và thu thập vũ khí mạnh.</t>
+          <t>Thông qua Convene, hòa nhịp với nhiều Resonator và Vũ Khí khác nhau. Đây là cách hiệu quả để gặp gỡ đồng minh đáng tin cậy và thu thập vũ khí mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Gặp gỡ các Rover khác trong Chế Độ Hợp Tác. Sự tử tế và thiện chí có thể mang đến cho bạn những tình bạn quý giá.</t>
+          <t>Gặp gỡ các Vận Mệnh Giả khác trong Chế Độ Hợp Tác. Lòng tốt và thiện chí có thể mang đến cho cậu những tình bạn quý giá.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Terminal của bạn được cài đặt các mô-đun cung cấp thông tin về Tacet Discord, Sinh Vật Đột Biến và Tacet Field. Hãy sử dụng các mô-đun này để nhanh chóng xác định vị trí mục tiêu.</t>
+          <t>Thiết bị đầu cuối của cậu được cài đặt các mô-đun cung cấp thông tin về Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Hãy dùng chúng để nhanh chóng xác định mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Trải nghiệm những câu chuyện độc đáo của Resonators.</t>
+          <t>Khám phá những câu chuyện độc đáo của các Resonator.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Các mô-đun trợ lý được cài đặt trong Terminal của bạn, được thiết kế cho nhiều tình huống khác nhau trong quá trình khám phá.</t>
+          <t>Các mô-đun hỗ trợ được cài đặt trong Thiết bị đầu cuối của cậu, phù hợp cho nhiều tình huống khác nhau trong quá trình khám phá.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hiệp hội Tiên Phong tạo ra Sonoro Sphere này để mô phỏng môi trường trong giếng sâu Tower of Adversity. Resonators có thể luyện tập tại đây trước khi thách thức Tower of Adversity thật sự.</t>
+          <t>Hiệp hội Tiên phong đã tạo ra Sonoro Sphere này để mô phỏng môi trường trong giếng sâu của Tháp Nghịch Cảnh. Các Resonator có thể luyện tập ở đây trước khi thử sức với Tháp Nghịch Cảnh thật sự.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Một trung tâm nghiên cứu ngầm rộng lớn được xây dựng trước Thương Khốc, nổi bật với giếng sâu xuống tới độ sâu của ranh giới Moho. Ở đáy giếng, vô số bí ẩn đang chờ được khám phá.</t>
+          <t>Một trung tâm nghiên cứu ngầm rộng lớn được xây dựng trước Lament, có giếng sâu xuống đến tận ranh giới Moho. Ở đáy giếng, vô số bí ẩn đang chờ được khám phá.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bạn có thể thu thập vật liệu Echo bằng cách hoàn thành Tacet Fields.</t>
+          <t>Cậu có thể thu thập vật liệu Echo bằng cách tiêu diệt Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Một phần của hệ thống hậu cần toàn diện do Bộ Phận Quân Nhu triển khai. Đây là máy in 3D đa chức năng mô-đun tiên tiến dùng để chế tạo linh kiện. Do đó, nó được gọi là "Print Crafter" hoặc "Bàn Chế Tạo".</t>
+          <t>Một phần của hệ thống hậu cần toàn diện do Bộ Hậu Cần triển khai. Đây là máy in 3D đa chức năng, mô-đun tiên tiến dùng để chế tạo linh kiện, nên còn được gọi là "Máy In Thủ Công" hay "Bàn Chế Tác".</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Obsolete</t>
+          <t>Lỗi Thời</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Pioneer Podcast để nhận Podcast EXP và nhiều phần thưởng khác.</t>
+          <t>Hoàn thành Nhiệm Vụ Podcast Tiên Phong để nhận Kinh Nghiệm Podcast và nhiều phần thưởng hấp dẫn.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhiều Resonators tạo nên Sonoro Spheres đều là bậc thầy về vũ khí. Những giai điệu trong lưỡi kiếm gãy của họ có thể dùng để tăng cường vũ khí.</t>
+          <t>Nhiều Resonator tạo nên Sonoro Spheres đều là những bậc thầy về vũ khí. Những giai điệu trong lưỡi kiếm gãy của họ có thể được dùng để nâng cao sức mạnh vũ khí.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nhiều Resonators tạo nên Sonoro Spheres đều là những bậc thầy về kỹ năng chiến đấu. Những giai điệu trong giấc mơ tan vỡ của họ có thể được dùng để tăng cường kỹ năng chiến đấu.</t>
+          <t>Nhiều Resonator tạo nên Sonoro Spheres đều là những bậc thầy về kỹ năng chiến đấu. Những giai điệu trong giấc mơ tan vỡ của họ có thể được dùng để nâng cao kỹ năng chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Bạn có khả năng hấp thụ và cộng hưởng với âm thanh của mọi thứ trên thế giới và thay đổi Attribute Cộng hưởng của mình.</t>
+          <t>Cậu có khả năng hấp thụ và cộng hưởng với âm thanh của vạn vật trên thế giới, thay đổi thuộc tính Cộng hưởng của chính mình.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Dự án nghiên cứu quy mô lớn do Huaxu Academy khởi xướng. Nhận thưởng khi vượt qua các thử thách trong Tower.</t>
+          <t>Dự án nghiên cứu quy mô lớn do Học viện Huaxu khởi xướng. Hoàn thành các thử thách trong Tháp để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Rover có thể nhận nhân vật, vũ khí và vật liệu Echo bằng cách vượt qua Sonoro Spheres.</t>
+          <t>Vận Mệnh Giả có thể nhận được nhân vật, vũ khí và nguyên liệu Echo bằng cách vượt qua các Sonoro Spheres.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Dữ liệu chiến đấu thu được từ Tactical Hologram: Calamity. Exchange chúng lấy nhiều phần thưởng khác nhau tại cửa hàng luyện tập.</t>
+          <t>Dữ liệu chiến đấu thu được từ Chiến thuật Hologram: Thảm họa. Đổi chúng lấy nhiều phần thưởng khác nhau trong cửa hàng luyện tập.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Bạn có thể nhận vật liệu thăng cấp nhân vật từ Thử thách Boss.</t>
+          <t>Cậu có thể nhận vật liệu thăng cấp nhân vật từ Thử Thách Trùm.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Trò chơi bài dành cho hai người. Để chiến thắng, bạn cần sự quan sát, chiến thuật và tất nhiên, một chút may mắn.</t>
+          <t>Trò chơi bài hai người. Để thắng, cậu cần sự quan sát, chiến thuật, và tất nhiên, một chút may mắn.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Khám phá nguyên liệu và hương vị yêu thích của bạn đồng hành qua cuộc trò chuyện, sau đó pha chế thức uống mà họ thích nhất.</t>
+          <t>Qua những cuộc trò chuyện, khám phá nguyên liệu và hương vị yêu thích của các Cộng Hưởng Giả đồng hành, rồi pha chế món đồ uống mà họ thích nhất.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Trong Trang trí Đội hình, bạn có thể nhận nhiều vật trang trí khác nhau và dùng chúng để tạo không khí đặc biệt cho buổi tiệc.</t>
+          <t>Trong Trang Trí Bữa Tiệc, bạn có thể thu thập nhiều loại vật phẩm trang trí và sử dụng chúng để tạo nên không khí đặc biệt cho buổi tiệc.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Một cuốn album ảnh do Copo Cobb tặng, chứa đựng những khoảnh khắc đẹp đẽ hiện ra qua từng trang lật.</t>
+          <t>Một cuốn album ảnh do Copo Cobb tặng, chứa đựng những khoảnh khắc đẹp đẽ hiện ra sau mỗi lần lật trang.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Một cuốn sách quảng cáo về Lollo Party. Trong những trang sách, những khoảnh khắc từ Forever Fest được lưu giữ, mỗi khoảnh khắc đều sẵn sàng bung tỏa niềm vui vô tận.</t>
+          <t>Một tờ quảng cáo của Lễ hội Lollo. Trong những trang giấy, những khoảnh khắc từ Forever Fest được lưu giữ, mỗi khoảnh khắc đều sẵn sàng bung nở thành niềm vui vô bờ.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Cửa hàng</t>
+          <t>Cửa Hàng</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Thành tựu</t>
+          <t>Cúp Chiến Thắng</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sổ tay</t>
+          <t>Sổ Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chế độ Hợp tác</t>
+          <t>Chế độ Đồng Đội</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Liên kết Email</t>
+          <t>Email Liên Kết</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tổng hợp</t>
+          <t>Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Kinh nghiệm Tiên Phong</t>
+          <t>Điểm Kinh Nghiệm Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>WavesLine</t>
+          <t>Đường Sóng</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Nằm sâu trong kho tàng Averardo, ngoài mạng lưới tàu Echo, tháp này ít người biết đến. Nơi đây ẩn chứa những bí mật đen tối nào?</t>
+          <t>Nằm sâu trong lòng Kho Tàng Averardo, ngoài mạng lưới tàu Echo, tháp này ít người biết đến. Nơi đây đang che giấu những bí mật đen tối nào?</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Huấn luyện Mô phỏng diễn ra trong một Sonoro Sphere nhân tạo dành cho tập luyện chiến đấu. Hoàn thành các thử thách để nhận nhiều tài nguyên khác nhau.</t>
+          <t>Huấn luyện mô phỏng diễn ra trong một Sonoro Sphere nhân tạo dành riêng cho tập luyện chiến đấu. Hoàn thành các thử thách để nhận nhiều tài nguyên khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Trên mảnh đất này có nhiều Sonoro Spheres nhân tạo được thiết lập để đáp ứng các nhu cầu khác nhau.</t>
+          <t>Trên vùng đất này có rất nhiều Sonoro Sphere nhân tạo, phục vụ cho nhiều nhu cầu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Trên mảnh đất này có nhiều Sonoro Spheres nhân tạo được thiết lập để đáp ứng các nhu cầu khác nhau.</t>
+          <t>Trên vùng đất này có rất nhiều Sonoro Sphere nhân tạo, phục vụ cho nhiều nhu cầu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Trong đống đổ nát, những cơn ác mộng hỗn loạn ẩn nấp trong bóng tối...</t>
+          <t>Trong đống hoang tàn, những cơn ác mộng hỗn loạn ẩn nấp trong bóng tối...</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bước lên toa tàu, một hành trình xuyên qua mạng lưới giấc mơ chằng chịt dần mở ra trước mắt bạn.</t>
+          <t>Khi bước lên toa tàu, một hành trình xuyên qua mê cung những giấc mơ mở ra trước mắt cậu.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Trên hồ, những lời thì thầm của giấc mơ không yên cứ nhẹ nhàng lướt vào tai bạn...</t>
+          <t>Trên mặt hồ, những lời thì thầm của những giấc mơ bất an khẽ lướt qua tai ngươi...</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Huấn luyện Mô phỏng diễn ra trong một Sonoro Sphere nhân tạo dành cho tập luyện chiến đấu. Hoàn thành các thử thách để nhận nhiều tài nguyên khác nhau.</t>
+          <t>Huấn luyện mô phỏng diễn ra trong một Sonoro Sphere nhân tạo dành riêng cho tập luyện chiến đấu. Hoàn thành các thử thách để nhận nhiều tài nguyên khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5580,8 +5580,8 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Âm nhạc vẫn tiếp tục, tấm màn đỏ sắp được kéo lên lần nữa.
-Ngươi có muốn cùng nàng nhảy thêm một điệu trong vở kịch dài bất tận này không?</t>
+          <t>Âm nhạc vẫn tiếp tục, bức màn đỏ sắp được kéo lên.
+Trong vở kịch dài bất tận này, ngươi có muốn cùng nàng nhảy thêm một điệu nữa không?</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Người ta nói rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
+          <t>Người ta kể rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Người ta nói rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
+          <t>Người ta kể rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Một công trình tôn giáo hai tầng ở Thành phố Ragunna, nơi thờ phụng bức tượng Người Bảo Hộ. Đây cũng là trụ sở của Dòng Trật Tự Vực Sâu.</t>
+          <t>Một công trình tôn giáo hai tầng ở Thành phố Ragunna, dành riêng cho việc thờ phụng bức tượng Sentinel. Đây cũng là trụ sở của Order of the Deep.</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Người ta nói rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
+          <t>Người ta kể rằng số phận của những người thừa kế Fisalia gắn liền với ba ngọn tháp sừng sững, và đây là một trong số đó.</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Phía sau tấm gương là một cõi giới nơi ảo ảnh quá khứ đan xen với hiện thực, nhưng con đường phía trước lại dẫn đến một định mệnh hoàn toàn khác.</t>
+          <t>Phía sau tấm gương là một cõi nơi ảo ảnh quá khứ đan xen với hiện thực, nhưng con đường phía trước lại dẫn đến một vận mệnh hoàn toàn khác biệt.</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Nhà tù xây bằng quyền lực và nỗi sợ đủ mạnh để trói buộc tâm trí—nhưng nó không thể át đi khúc ca vang lên từ trái tim con người.</t>
+          <t>Nhà tù xây bằng quyền lực và nỗi sợ đủ mạnh để trói buộc tâm trí—nhưng không thể bịt miệng khúc ca trỗi dậy từ trái tim con người.</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn đã xuất hiện, dẫn đến một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris...</t>
+          <t>Một cánh cổng bí ẩn đã xuất hiện, dẫn đến cõi Somnoire. Truyền thuyết kể rằng nơi đây lưu giữ giấc mơ của tất cả sinh linh trên Solaris...</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Giao Hòm</t>
+          <t>Nâng Cấp Giao Hàng Quan Tài</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Phần thưởng Tháp Nghịch Cảnh</t>
+          <t>Phần Thưởng Tháp Thử Thách</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Độ Khó New trong Chiến Thuật Hologram: Calamity</t>
+          <t>Mức Độ Mới Trong Chiến Thuật Hologram: Tai Họa</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Challenges New Trong Chiến Thuật Hologram: Phantom Pain</t>
+          <t>Thử Thách Mới trong Chiến Thuật Hologram: Phantom Pain</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Giao Hòm Septimont</t>
+          <t>Nâng Cấp Rương Sonance Septimont</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Giao Hòm Ragunna</t>
+          <t>Nâng Cấp Cấp Độ Giao Hàng Quan Tài Ragunna</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cài đặt đầu vào</t>
+          <t>Thiết Lập Nhập Liệu</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Điều Tiết Hoàn Toàn</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Một phần</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đi</t>
+          <t>Đi thôi</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Needle Joystick tĩnh</t>
+          <t>Tay Cầm Tĩnh</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Needle Joystick động</t>
+          <t>Tay cầm Điều khiển Động</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Tài khoản</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Ctrl trái</t>
+          <t>Ctrl Trái</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Bánh xe chuột</t>
+          <t>Bánh Xe Chuột</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Giữ Wheel Chuột</t>
+          <t>Giữ nút cuộn chuột</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Shift trái</t>
+          <t>Shift Trái</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Nhấp Chuột Right</t>
+          <t>Nhấp Chuột Phải</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Không Gian</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Nhấp Chuột Right</t>
+          <t>Nhấp Chuột Phải</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Ôi</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>简体中文</t>
+          <t>Tiếng Trung Giản Thể</t>
         </is>
       </c>
     </row>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tiếng Anh</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>Tiếng Nhật</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Tiếng Nga</t>
+          <t>русский язык</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>繁體中文</t>
+          <t>Tiếng Trung phồn thể</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Español</t>
+          <t>Tiếng Tây Ban Nha</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Tiếng Indonesia</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Language Text</t>
+          <t>Ngôn ngữ Văn bản</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Quả quýt</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tiếng Anh</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Tiếng Nhật</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Language Lồng Tiếng</t>
+          <t>Ngôn Ngữ Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Language Lồng Tiếng</t>
+          <t>Ngôn Ngữ Lồng Tiếng</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Cơ bản</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Cơ bản</t>
         </is>
       </c>
     </row>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Siêu Cao</t>
+          <t>Siêu Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Siêu Cao</t>
+          <t>Siêu Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Chức Năng Hệ thống</t>
+          <t>Chức Năng Hệ Thống</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Toàn màn hình</t>
+          <t>Toàn Màn Hình</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chế độ cửa sổ</t>
+          <t>Chế Độ Cửa Sổ</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Cơ bản</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>H...</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Cơ bản</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Rất thấp</t>
+          <t>Rất Thấp</t>
         </is>
       </c>
     </row>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Tiến Hóa</t>
         </is>
       </c>
     </row>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Hiệu Suất Siêu Cao</t>
+          <t>Hiệu Suất Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Biểu diễn</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Cân bằng</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Chất lượng</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Chất Lượng Siêu Cao</t>
+          <t>Chất Lượng Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hiệu Suất Siêu Cao</t>
+          <t>Hiệu Suất Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Biểu diễn</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Cân bằng</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Chất lượng</t>
         </is>
       </c>
     </row>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Quality cao</t>
+          <t>Chất Lượng Cao</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Chất Lượng Siêu Cao</t>
+          <t>Chất Lượng Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Cơ bản</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Âm Lượng</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Rất cao</t>
+          <t>Rất Cao</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Hiệu suất và Kinh nghiệm</t>
+          <t>Hiệu Suất và Trải Nghiệm</t>
         </is>
       </c>
     </row>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -18971,7 +18971,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Hiệu suất và Kinh nghiệm</t>
+          <t>Hiệu Suất và Trải Nghiệm</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Tai nghe</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Người nói</t>
         </is>
       </c>
     </row>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Hiệu suất và Kinh nghiệm</t>
+          <t>Hiệu Suất và Trải Nghiệm</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Âm thanh vòm</t>
+          <t>Âm Thanh Vòm</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Hiệu suất và Kinh nghiệm</t>
+          <t>Hiệu Suất và Trải Nghiệm</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -19621,7 +19621,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Off một phần</t>
+          <t>Tắt một phần</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -20466,7 +20466,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Tự động</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Chất lượng</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Cân bằng</t>
         </is>
       </c>
     </row>
@@ -21181,7 +21181,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Biểu diễn</t>
         </is>
       </c>
     </row>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Hiệu suất Tối ưu</t>
+          <t>Biểu Diễn Tối Thượng</t>
         </is>
       </c>
     </row>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Chất lượng Tối ưu</t>
+          <t>Chất Lượng Tối Thượng</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Chất lượng Tối ưu+</t>
+          <t>Chất Lượng Tối Thượng+</t>
         </is>
       </c>
     </row>
@@ -21506,7 +21506,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Chất lượng Tối ưu+Khử răng cưa</t>
+          <t>Chất Lượng Tối Thượng+Khử Răng Cưa</t>
         </is>
       </c>
     </row>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Bật + Boost</t>
+          <t>Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đến Cài đặt</t>
+          <t>Vào Cài Đặt</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -22221,7 +22221,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Rover (Nữ)</t>
+          <t>Vận Mệnh Giả (Nữ)</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Rover (Nam)</t>
+          <t>Vận Mệnh Giả (Nam)</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Setting người chơi</t>
+          <t>Cài Đặt Người Chơi</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22676,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Cài đặt Camera</t>
+          <t>Cài đặt máy quay</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -23131,7 +23131,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
     </row>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Bảng Nâng cấp Băng</t>
+          <t>Bảng Nâng Cấp Băng</t>
         </is>
       </c>
     </row>
@@ -23456,7 +23456,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Bảng Chuyển đổi Băng</t>
+          <t>Bảng Chuyển Đổi Băng</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -23911,7 +23911,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Thăng hoa</t>
         </is>
       </c>
     </row>
@@ -23976,7 +23976,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tune</t>
+          <t>Điệu nhạc</t>
         </is>
       </c>
     </row>
@@ -24301,7 +24301,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Trưng bày Resonator</t>
+          <t>Trình diễn Resonator</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Sổ Ấn Ký Travel</t>
+          <t>Sổ Ấn Du Hành</t>
         </is>
       </c>
     </row>
@@ -24496,7 +24496,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Tuning Echo</t>
+          <t>Điều Chỉnh Tiếng Vọng</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -24821,7 +24821,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Podcast</t>
+          <t>Nhiệm Vụ Podcast</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Vật phẩm Chiến đấu</t>
+          <t>Vật Tư Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -25146,7 +25146,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Thăng hoa</t>
         </is>
       </c>
     </row>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
     </row>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Trang phục Resonator</t>
+          <t>Trang Phục Resonator</t>
         </is>
       </c>
     </row>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Diện mạo Echo</t>
+          <t>Thuộc Tính Echo</t>
         </is>
       </c>
     </row>
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Đang áp dụng thiết lập...</t>
+          <t>Đang thiết lập...</t>
         </is>
       </c>
     </row>
@@ -25536,7 +25536,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Edit Trưng bày</t>
+          <t>Chỉnh sửa trưng bày</t>
         </is>
       </c>
     </row>
@@ -25601,7 +25601,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Không có Resonator nào được hiển thị</t>
+          <t>Không hiển thị Resonator</t>
         </is>
       </c>
     </row>
@@ -25666,7 +25666,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -25796,7 +25796,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Hiệu Suất Siêu Cao</t>
+          <t>Hiệu Suất Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Biểu diễn</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Chất lượng</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Chất Lượng Siêu Cao</t>
+          <t>Chất Lượng Siêu Cấp</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro của Sentinel Jué. Nơi bình minh và hoàng hôn đan xen, bốn mùa đảo lộn, là chốn bao trùm khởi đầu và kết thúc của mọi thời gian.</t>
+          <t>Cầu Siêu Âm của Kẻ Canh Gác Jué. Nơi bình minh và hoàng hôn đan xen, bốn mùa đảo lộn, là chốn bao trùm khởi đầu và kết thúc của mọi thời gian.</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Nâng Cấp Trung Tâm Dữ Liệu</t>
+          <t>Nâng cấp Trung tâm dữ liệu</t>
         </is>
       </c>
     </row>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Hướng Movement</t>
+          <t>Hướng Di Chuyển</t>
         </is>
       </c>
     </row>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hướng Camera</t>
+          <t>Điều khiển máy quay</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Distance</t>
+          <t>Khoảng cách</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
     </row>
@@ -26706,7 +26706,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Đảo ngược Lên/Xuống</t>
+          <t>Đảo Ngược Lên/Xuống</t>
         </is>
       </c>
     </row>
@@ -26771,7 +26771,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Khi bật, Graphics Quality và FPS tối đa sẽ tự động giảm nếu cấu hình hiện tại quá tải.</t>
+          <t>Khi bật, Chất lượng Đồ họa và FPS tối đa sẽ tự động giảm nếu cấu hình hiện tại quá tải.</t>
         </is>
       </c>
     </row>
@@ -26901,7 +26901,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Bật Auto FPS</t>
+          <t>Bật Tự Động Điều Chỉnh FPS</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Đi</t>
+          <t>Đi thôi</t>
         </is>
       </c>
     </row>
@@ -27096,7 +27096,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Toàn màn hình</t>
+          <t>Toàn Màn Hình</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Letterbox</t>
+          <t>Hòm Thư</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Interface HUD</t>
+          <t>Giao diện HUD</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Điều khiển lên/xuống khi Flight sẽ bị đảo ngược.</t>
+          <t>Điều khiển lên/xuống khi Bay sẽ bị đảo ngược.</t>
         </is>
       </c>
     </row>
@@ -27356,7 +27356,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Tiến Hóa</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Ray Tracing (Ray Tracing)</t>
+          <t>Dò tia</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Bật Ray Tracing để render phản chiếu vật thể chính xác hơn trên các bề mặt phản chiếu trong game.</t>
+          <t>Bật Tính Năng Dò Tia để tái tạo phản chiếu chính xác hơn của vật thể trên các bề mặt phản chiếu trong trò chơi.</t>
         </is>
       </c>
     </row>
@@ -27551,7 +27551,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bật Tính Năng Dò Tia để tính toán ánh sáng gián tiếp, mang lại hiệu ứng ánh sáng chân thực hơn trong game. Cài đặt càng cao, yêu cầu hiệu năng càng lớn.</t>
+          <t>Bật Tính Năng Dò Tia để tính toán ánh sáng gián tiếp, mang lại hiệu ứng ánh sáng chân thực hơn trong trò chơi. Cài đặt càng cao, chi phí hiệu năng càng lớn.</t>
         </is>
       </c>
     </row>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Bật Ray Tracing để cải thiện chất lượng đổ bóng trong game.</t>
+          <t>Bật Tính Năng Dò Tia để cải thiện chất lượng đổ bóng trong trò chơi.</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Bạn đã mở khóa Baiting. Hãy sử dụng khi ở trên Rachel để tạo Điểm Fishing lý tưởng.</t>
+          <t>Bạn đã mở khóa Kỹ Năng Dụ Cá. Hãy sử dụng khi ở trên Rachel để tạo Điểm Câu Cá lý tưởng.</t>
         </is>
       </c>
     </row>
@@ -27746,7 +27746,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Bạn đã mở khóa Đèn Hàng Hải. Sử dụng khi ở trên Rachel để xua đuổi Ghost Medusa gần đó.</t>
+          <t>Bạn đã mở khóa Đèn Hàng Hải. Hãy sử dụng khi ở trên Rachel để xua đuổi Ghost Medusa gần đó.</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Bạn đã mở khóa Sweet Puff. Sử dụng khi ở trên Rachel để bắn các Fishing Spots Cá gần đó và thu thập trực tiếp chiến lợi phẩm tương ứng.</t>
+          <t>Bạn đã mở khóa Bánh Ngọt Bùng Nổ. Hãy sử dụng khi ở trên Rachel để kích nổ Điểm Câu Cá gần đó và thu hoạch cá trực tiếp.</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Bạn đã mở khóa Di Chuyển Nhanh đến Dock. Sử dụng khi ở trên Rachel để di chuyển nhanh đến bến tàu trước đó bạn đã ghé thăm.</t>
+          <t>Bạn đã mở khóa Dịch Chuyển Nhanh Đến Bến cảng. Hãy sử dụng khi ở trên Rachel để dịch chuyển nhanh đến bến tàu gần nhất bạn đã ghé thăm.</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
     </row>
@@ -28006,7 +28006,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Screenplay</t>
+          <t>Kịch Bản</t>
         </is>
       </c>
     </row>
@@ -28071,7 +28071,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Hậu trường</t>
+          <t>Hậu Trường</t>
         </is>
       </c>
     </row>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -28201,7 +28201,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Off một phần</t>
+          <t>Tắt một phần</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Quản lý Tài nguyên Game</t>
+          <t>Quản Lý Tài Nguyên Trò Chơi</t>
         </is>
       </c>
     </row>
@@ -28396,7 +28396,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Khi bật, các đối tượng môi trường sẽ phản ứng vật lý dựa trên hành động của người chơi, như tấn công và kỹ năng. Hiệu ứng sẽ tự động điều chỉnh theo cài đặt đồ họa.</t>
+          <t>Khi bật lên, các vật thể trong môi trường sẽ phản ứng vật lý dựa trên hành động của người chơi, như tấn công hay kỹ năng. Hiệu ứng sẽ tự động điều chỉnh theo cài đặt đồ họa.</t>
         </is>
       </c>
     </row>
@@ -28461,7 +28461,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Khi tùy chọn này được bật, Resonator sẽ duy trì trạng thái Sprinting cho đến khi bị gián đoạn bởi các hành động khác.</t>
+          <t>Khi tùy chọn này được bật, khi Resonator bắt đầu Chạy Nước Rút, họ sẽ duy trì trạng thái này cho đến khi bị gián đoạn bởi các hành động khác.</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Khi tùy chọn này được bật, Resonator sẽ tăng tốc và bắt đầu Chạy Nước Rút nếu tiếp tục chạy trong một khoảng thời gian.</t>
+          <t>Khi tùy chọn này được bật, Resonator sẽ tăng tốc và bắt đầu Chạy Nước Rút nếu tiếp tục chạy một lúc.</t>
         </is>
       </c>
     </row>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Cài đặt tốc độ khung hình tối đa sẽ bị vô hiệu hóa nếu Frame Generation được bật.</t>
+          <t>Cài đặt tốc độ khung hình tối đa sẽ bị vô hiệu hóa nếu tính năng Tạo Khung Hình được bật.</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bộ lọc hiệu ứng không ảnh hưởng đến các thành phần UI và cảnh cắt.</t>
+          <t>Bộ lọc không ảnh hưởng đến các thành phần giao diện và cảnh cắt.</t>
         </is>
       </c>
     </row>
@@ -28721,7 +28721,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Công nghệ đồ họa thế hệ mới hỗ trợ các tính năng đồ họa tiên tiến để tối ưu hiệu suất mượt mà và hiệu quả tài nguyên. Restart ứng dụng để thay đổi có hiệu lực.</t>
+          <t>Công nghệ đồ họa thế hệ mới hỗ trợ các tính năng đồ họa tiên tiến, giúp hiệu suất mượt mà hơn và tối ưu tài nguyên tốt hơn. Khởi động lại ứng dụng để áp dụng thay đổi.</t>
         </is>
       </c>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Challenges Định Kỳ đã làm mới</t>
+          <t>Thử Thách Lặp Lại đã được làm mới</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Cài đặt Độ An Toàn Mắt không ảnh hưởng đến các thành phần UI và cảnh cắt cảnh.</t>
+          <t>Chế độ chăm sóc mắt không ảnh hưởng đến các thành phần giao diện và cảnh cắt.</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -29111,7 +29111,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Siêu Cao</t>
+          <t>Siêu Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -29176,7 +29176,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Áp dụng hiệu ứng trong suốt một phần khi camera đi vào tán lá.</t>
+          <t>Áp dụng hiệu ứng trong suốt khi camera đi vào tán lá.</t>
         </is>
       </c>
     </row>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Light Rực Rỡ</t>
+          <t>Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
     </row>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Ánh sáng Yếu</t>
+          <t>Ánh Sáng Yếu</t>
         </is>
       </c>
     </row>
@@ -29436,7 +29436,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Tùy chỉnh</t>
         </is>
       </c>
     </row>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>2 lần</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
     </row>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Chế độ護 mắt</t>
+          <t>Chế Độ Chăm Sóc Mắt</t>
         </is>
       </c>
     </row>
@@ -29956,7 +29956,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Trạm Switch Đổi</t>
+          <t>Chuyển Thiết bị Đầu Cuối</t>
         </is>
       </c>
     </row>
@@ -30021,7 +30021,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Kích hoạt Adaptive Triggers trên tay cầm khi bật. Lưu ý rằng chức năng này chỉ khả dụng ở một số phần của trò chơi.</t>
+          <t>Kích hoạt nút Adaptive Triggers trên tay cầm khi bật. Lưu ý rằng chức năng này chỉ khả dụng trong một số phần của trò chơi.</t>
         </is>
       </c>
     </row>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Ngọn lửa sáng rực chiếu sáng mọi ngóc ngách của Hẻm Đen, không để lại bóng tối nào có thể ẩn náu.</t>
+          <t>Ngọn lửa rực rỡ soi sáng từng ngóc ngách Hẻm Đen, không để lại một bóng tối nào ẩn náu.</t>
         </is>
       </c>
     </row>
@@ -30476,7 +30476,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Khi tiếng sấm vang lên, tuyết mùa đông tan biến dưới ánh sáng thoáng qua.</t>
+          <t>Nghe tiếng sấm vang, tuyết mùa đông tan biến dưới ánh sáng thoáng qua.</t>
         </is>
       </c>
     </row>
@@ -30541,7 +30541,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Kẻ trở về từ vực thẳm sẽ thanh tẩy thế gian này bằng địa ngục lửa.</t>
+          <t>Kẻ trở về từ vực thẳm sẽ thanh tẩy thế giới này bằng ngọn lửa địa ngục.</t>
         </is>
       </c>
     </row>
@@ -30672,8 +30672,8 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Âm nhạc vẫn chưa kết thúc. Bức màn đỏ sắp lại được kéo lên.
-Trên sân khấu dài lâu này, sao không nhảy thêm một điệu cùng cô ấy?</t>
+          <t>Bản nhạc vẫn chưa kết thúc. Bức màn đỏ sắp lại được kéo lên.
+Trên sân khấu bất tận này, sao không cùng nàng nhảy thêm một điệu nữa?</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Khu vực này lưu giữ thành tựu nghiên cứu quan trọng nhất trước Lament của SkyArk—một nguyên mẫu Thiết bị Truyền Khối lượng sử dụng Giọt Etheric Sea.</t>
+          <t>Khu vực này lưu giữ thành tựu nghiên cứu quan trọng nhất của SkyArk trước Thảm Họa Lament—một nguyên mẫu Thiết bị Truyền Khối lượng vận hành bằng Giọt Biển Ether.</t>
         </is>
       </c>
     </row>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Nơi đây từng có một lễ hội vĩnh cửu, nhưng rồi một ngày cũng sẽ kết thúc.</t>
+          <t>Nơi đó có một lễ hội vĩnh cửu, nhưng rồi một ngày cũng sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tuyết nhẹ nhàng rơi xuống mặt đất, mang theo số phận đan xen của những người bước đi trên tuyết.</t>
+          <t>Tuyết mịn rơi nhẹ nhàng xuống đất, mang theo số phận đan xen của những kẻ bước đi trên tuyết.</t>
         </is>
       </c>
     </row>
@@ -30933,7 +30933,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Nơi đây, những giọng nói phai nhạt và những lối mòn ẩn giấu được dệt thành một mạng lưới, và lý lẽ của vàng lỏng đang được kiên nhẫn gỡ rối…</t>
+          <t>Nơi đây, những giọng nói phai mờ và con đường ẩn giấu đan xen thành một mạng lưới, còn lý lẽ của vàng lỏng thì kiên nhẫn được gỡ bỏ…</t>
         </is>
       </c>
     </row>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Mỗi học sinh bước vào Startorch Academy đều mang theo một trái tim chân thành.
+          <t>Mỗi học viên bước vào Học viện Startorch đều mang theo một trái tim chân thành.
 Những trái tim như vậy là báu vật không bao giờ được phép bị vấy bẩn.</t>
         </is>
       </c>
@@ -31065,7 +31065,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Vách đá sâu trong Lahai-Roi bị Voidmatter xâm thực. Nơi đây, ngay cả âm thanh cũng bị nuốt chửng.</t>
+          <t>Vách đá sâu trong lòng Lahai-Roi, nơi bị Voidmatter xâm thực. Âm thanh tại đây cũng bị nuốt chửng.</t>
         </is>
       </c>
     </row>
@@ -31130,7 +31130,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Những loài thực vật cổ xưa, thức tỉnh sau vô số kỷ nguyên, mọc lên với hình dạng không thuộc về thời đại này. Dưới ánh cực quang biến ảo, một tấm màn mơ hồ phủ xuống những bí mật quá cũ kỹ để kể lại.</t>
+          <t>Cây cổ thức tỉnh sau ngàn năm, mọc lên với hình hài không thuộc về thời đại này. Dưới ánh cực quang biến ảo, một màn sương mơ hồ phủ xuống những bí mật quá cũ để kể lại.</t>
         </is>
       </c>
     </row>
@@ -31196,8 +31196,8 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>—Viết nguệch ngoạc trên bảng tin với Dodget chữ không đều—
-"Đừng quên nỗi hối hận đã đưa bạn đến nơi đây."</t>
+          <t>—Ghi vội trên bảng tin bằng những nét chữ nguệch ngoạc—
+"Đừng quên nỗi hối hận đã đưa ngươi đến đây."</t>
         </is>
       </c>
     </row>
@@ -31262,7 +31262,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Nơi đây, quá khứ và hiện tại giao hòa, thời gian và không gian tan biến thành hỗn loạn.</t>
+          <t>Nơi đây, quá khứ và hiện tại giao thoa, thời gian và không gian tan rã thành hỗn loạn.</t>
         </is>
       </c>
     </row>
@@ -31328,8 +31328,8 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Nó nuốt chửng mọi thứ. Suy nghĩ, cảm xúc, hy vọng, tất cả đều hóa thành tro bụi và hư vô.
-Đó là Hư Không.</t>
+          <t>Nó nuốt chửng tất cả. Suy nghĩ, cảm xúc, hy vọng, tất cả đều tan thành tro bụi.
+Đó chính là Hư Không.</t>
         </is>
       </c>
     </row>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Để chứng minh họ có thể chịu đựng tải trọng thần kinh cực hạn khi kết nối với Exostrider, các Synchronist phải vượt qua bài test đồng bộ hóa.
+          <t>Để chứng minh họ chịu được tải thần kinh cực hạn khi kết nối với Exostrider, các Đồng Bộ Giả phải vượt qua bài kiểm tra đồng bộ hóa.
 Tất cả vì ngọn đuốc nhân loại.</t>
         </is>
       </c>
@@ -31721,7 +31721,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khi bật, game sẽ không phát âm thanh nếu thu nhỏ xuống taskbar hoặc chạy ngầm.</t>
+          <t>Khi bật, trò chơi sẽ không phát âm thanh nếu bị thu nhỏ xuống thanh tác vụ hoặc chạy ngầm.</t>
         </is>
       </c>
     </row>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Xe máy Thám Hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Một phương tiện di chuyển đa địa hình nhẹ, đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật Chất Hư Không của Startorch Academy. Là công cụ không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của sinh viên và giảng viên.</t>
+          <t>Một phương tiện địa hình nhẹ được đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật chất Hư không của Học viện Startorch. Không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của giảng viên và sinh viên.</t>
         </is>
       </c>
     </row>
@@ -31916,7 +31916,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Modality</t>
+          <t>Phương Thức</t>
         </is>
       </c>
     </row>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Mounted</t>
+          <t>Đã chiếm lĩnh</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Cài đặt Điều khiển Phương tiện</t>
+          <t>Cài Đặt Điều Khiển Phương Tiện</t>
         </is>
       </c>
     </row>
@@ -32111,7 +32111,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt, Acceleration sẽ duy trì trạng thái hoạt động và có thể bật/tắt bằng một lần nhấn.</t>
+          <t>Khi kích hoạt, Tăng Tốc sẽ duy trì sau khi được kích phát và có thể bật/tắt bằng một lần nhấn.</t>
         </is>
       </c>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Khi kích hoạt, Boost sẽ duy trì trạng thái hoạt động và có thể bật/tắt bằng một lần nhấn.</t>
+          <t>Khi được kích hoạt, Boost sẽ duy trì trạng thái hoạt động sau khi được kích và có thể bật/tắt chỉ bằng một lần nhấn.</t>
         </is>
       </c>
     </row>
@@ -32241,7 +32241,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt, Tăng Tốc sẽ duy trì khi trượt.</t>
+          <t>Khi kích hoạt, Tăng Tốc sẽ được duy trì trong khi trượt.</t>
         </is>
       </c>
     </row>
@@ -32306,7 +32306,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt, Tăng Tốc sẽ duy trì khi trượt.</t>
+          <t>Khi kích hoạt, Tăng Tốc sẽ được duy trì trong khi trượt.</t>
         </is>
       </c>
     </row>
@@ -32371,7 +32371,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khi bật, bảng điều khiển phương tiện sẽ không hiển thị.</t>
+          <t>Khi kích hoạt, bảng điều khiển của phương tiện sẽ không hiển thị.</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Nâng Cấp Cấp Độ Giao Hàng Cuộn Tape of Last Words</t>
+          <t>Lahai-Roi: Nâng Cấp Giao Hàng Cuộn Băng Lời Cuối</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Giao Hạt Soliseed</t>
+          <t>Nâng Cấp Cấp Độ Giao Hàng Soliseed</t>
         </is>
       </c>
     </row>
@@ -32631,7 +32631,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -32826,7 +32826,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -32891,7 +32891,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Stick</t>
+          <t>Cây gậy</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Nút bấm &amp; Vuốt</t>
+          <t>Nút Bấm &amp; Vuốt</t>
         </is>
       </c>
     </row>
@@ -33021,7 +33021,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Nếu điều khiển Xe được đặt ở chế độ Stick, vị trí và kích thước của cần điều khiển trong bố cục sẽ giữ nguyên như cài đặt Thông thường.</t>
+          <t>Nếu điều khiển Phương Tiện được đặt ở chế độ Stick, vị trí và kích thước của cần điều khiển trong bố cục sẽ giữ nguyên như cài đặt Regular.</t>
         </is>
       </c>
     </row>
